--- a/e2e/expectedData/rekap_bayar_Rekap_Pembayaran_2026-01.xlsx
+++ b/e2e/expectedData/rekap_bayar_Rekap_Pembayaran_2026-01.xlsx
@@ -50,7 +50,7 @@
     <t>Salary Cash - CASH</t>
   </si>
   <si>
-    <t>$ 20377.665</t>
+    <t>$ 22998.635</t>
   </si>
   <si>
     <t>cek sendiri</t>
@@ -59,10 +59,10 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>$ 21366.665</t>
-  </si>
-  <si>
-    <t>DILI, 26 August 2026</t>
+    <t>$ 23987.635</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/rekap_bayar_Rekap_Pembayaran_2026-01.xlsx
+++ b/e2e/expectedData/rekap_bayar_Rekap_Pembayaran_2026-01.xlsx
@@ -50,7 +50,7 @@
     <t>Salary Cash - CASH</t>
   </si>
   <si>
-    <t>$ 22998.635</t>
+    <t>$ 20966.635</t>
   </si>
   <si>
     <t>cek sendiri</t>
@@ -59,10 +59,10 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>$ 23987.635</t>
-  </si>
-  <si>
-    <t>DILI, 09 September 2026</t>
+    <t>$ 21955.635</t>
+  </si>
+  <si>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
